--- a/output/graficos_dimensiones/comunal_d_dep_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:01</t>
+    <t xml:space="preserve">2026-09-10 01:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:13</t>
+    <t xml:space="preserve">2026-09-12 22:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:25</t>
+    <t xml:space="preserve">2026-09-23 23:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 23:54</t>
+    <t xml:space="preserve">2026-10-02 15:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2024_nuble.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Yungay</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">San Carlos</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:56</t>
+    <t xml:space="preserve">2026-10-04 10:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:37</t>
+    <t xml:space="preserve">2026-10-05 16:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
